--- a/fine_tuning/text_evaluation_metrics/2026.08.12_test_all_metrics_summary.xlsx
+++ b/fine_tuning/text_evaluation_metrics/2026.08.12_test_all_metrics_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\#_Work\#_ОИПИ\Проекты\2021.11.03 ISTC-PR150\_Reports\2026-Q4\Scripts\Kosareva_metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC8B0FE-E43A-4BE7-94F5-F0E82D9DEE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74175341-D71B-4BFA-8732-C0C04EA72D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -418,12 +418,6 @@
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -435,6 +429,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -879,22 +879,22 @@
       <c r="E2" s="23"/>
       <c r="F2" s="23"/>
       <c r="G2" s="24"/>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13" t="s">
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13" t="s">
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
     </row>
     <row r="3" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="19" t="s">
@@ -993,7 +993,7 @@
       </c>
     </row>
     <row r="5" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1043,7 +1043,7 @@
       </c>
     </row>
     <row r="6" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="15"/>
+      <c r="B6" s="13"/>
       <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
@@ -1091,7 +1091,7 @@
       </c>
     </row>
     <row r="7" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="15"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
@@ -1139,7 +1139,7 @@
       </c>
     </row>
     <row r="8" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="15"/>
+      <c r="B8" s="13"/>
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
@@ -1187,7 +1187,7 @@
       </c>
     </row>
     <row r="9" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="15"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
@@ -1283,7 +1283,7 @@
       </c>
     </row>
     <row r="11" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1333,7 +1333,7 @@
       </c>
     </row>
     <row r="12" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="15"/>
+      <c r="B12" s="13"/>
       <c r="C12" s="2" t="s">
         <v>23</v>
       </c>
@@ -1381,7 +1381,7 @@
       </c>
     </row>
     <row r="13" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="15"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="2" t="s">
         <v>24</v>
       </c>
@@ -1429,7 +1429,7 @@
       </c>
     </row>
     <row r="14" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="15"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="2" t="s">
         <v>25</v>
       </c>
@@ -1477,7 +1477,7 @@
       </c>
     </row>
     <row r="15" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="15"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="2" t="s">
         <v>26</v>
       </c>
@@ -1525,7 +1525,7 @@
       </c>
     </row>
     <row r="16" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="15"/>
+      <c r="B16" s="13"/>
       <c r="C16" s="2" t="s">
         <v>27</v>
       </c>
@@ -1573,7 +1573,7 @@
       </c>
     </row>
     <row r="17" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="15"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="2" t="s">
         <v>28</v>
       </c>
@@ -1621,7 +1621,7 @@
       </c>
     </row>
     <row r="18" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -1671,7 +1671,7 @@
       </c>
     </row>
     <row r="19" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="15"/>
+      <c r="B19" s="13"/>
       <c r="C19" s="2" t="s">
         <v>19</v>
       </c>
@@ -1719,7 +1719,7 @@
       </c>
     </row>
     <row r="20" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="15"/>
+      <c r="B20" s="13"/>
       <c r="C20" s="2" t="s">
         <v>20</v>
       </c>
@@ -1775,22 +1775,22 @@
       <c r="E23" s="23"/>
       <c r="F23" s="23"/>
       <c r="G23" s="24"/>
-      <c r="H23" s="14" t="s">
+      <c r="H23" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13" t="s">
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13" t="s">
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18"/>
     </row>
     <row r="24" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="19" t="s">
@@ -1889,7 +1889,7 @@
       </c>
     </row>
     <row r="26" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -1939,7 +1939,7 @@
       </c>
     </row>
     <row r="27" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="17"/>
+      <c r="B27" s="15"/>
       <c r="C27" s="2" t="s">
         <v>14</v>
       </c>
@@ -1987,7 +1987,7 @@
       </c>
     </row>
     <row r="28" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="17"/>
+      <c r="B28" s="15"/>
       <c r="C28" s="2" t="s">
         <v>15</v>
       </c>
@@ -2035,7 +2035,7 @@
       </c>
     </row>
     <row r="29" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="17"/>
+      <c r="B29" s="15"/>
       <c r="C29" s="2" t="s">
         <v>16</v>
       </c>
@@ -2083,7 +2083,7 @@
       </c>
     </row>
     <row r="30" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="17"/>
+      <c r="B30" s="15"/>
       <c r="C30" s="2" t="s">
         <v>17</v>
       </c>
@@ -2131,7 +2131,7 @@
       </c>
     </row>
     <row r="31" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="18"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="2" t="s">
         <v>31</v>
       </c>
@@ -2179,7 +2179,7 @@
       </c>
     </row>
     <row r="32" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -2229,7 +2229,7 @@
       </c>
     </row>
     <row r="33" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="15"/>
+      <c r="B33" s="13"/>
       <c r="C33" s="2" t="s">
         <v>23</v>
       </c>
@@ -2277,7 +2277,7 @@
       </c>
     </row>
     <row r="34" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="15"/>
+      <c r="B34" s="13"/>
       <c r="C34" s="2" t="s">
         <v>24</v>
       </c>
@@ -2325,7 +2325,7 @@
       </c>
     </row>
     <row r="35" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="15"/>
+      <c r="B35" s="13"/>
       <c r="C35" s="2" t="s">
         <v>25</v>
       </c>
@@ -2373,7 +2373,7 @@
       </c>
     </row>
     <row r="36" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="15"/>
+      <c r="B36" s="13"/>
       <c r="C36" s="2" t="s">
         <v>26</v>
       </c>
@@ -2421,7 +2421,7 @@
       </c>
     </row>
     <row r="37" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="15"/>
+      <c r="B37" s="13"/>
       <c r="C37" s="2" t="s">
         <v>27</v>
       </c>
@@ -2469,7 +2469,7 @@
       </c>
     </row>
     <row r="38" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="15"/>
+      <c r="B38" s="13"/>
       <c r="C38" s="2" t="s">
         <v>28</v>
       </c>
@@ -2517,7 +2517,7 @@
       </c>
     </row>
     <row r="39" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -2567,7 +2567,7 @@
       </c>
     </row>
     <row r="40" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="15"/>
+      <c r="B40" s="13"/>
       <c r="C40" s="2" t="s">
         <v>19</v>
       </c>
@@ -2615,7 +2615,7 @@
       </c>
     </row>
     <row r="41" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="15"/>
+      <c r="B41" s="13"/>
       <c r="C41" s="2" t="s">
         <v>20</v>
       </c>
@@ -2667,6 +2667,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:Q23"/>
     <mergeCell ref="B39:B41"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B11:B17"/>
@@ -2682,11 +2687,6 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:Q23"/>
   </mergeCells>
   <conditionalFormatting sqref="I25:I41">
     <cfRule type="colorScale" priority="188">
